--- a/Indomie Clients Details/Gourmet - 17-06-26.xlsx
+++ b/Indomie Clients Details/Gourmet - 17-06-26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B5C911-2E0B-4B41-9765-4FAE3669F602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14BA8CB-464C-4C8C-885A-AFA527807FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,7 +3898,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -3926,7 +3926,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -5139,7 +5139,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -5167,7 +5167,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -6380,7 +6380,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -6408,7 +6408,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -7620,7 +7620,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -7648,7 +7648,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -8862,7 +8862,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -8890,7 +8890,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -10097,7 +10097,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -10125,7 +10125,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -11377,7 +11377,7 @@
       <c r="M4" s="356"/>
       <c r="N4" s="357">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="357"/>
       <c r="P4" s="357"/>
@@ -11411,7 +11411,7 @@
       <c r="M5" s="356"/>
       <c r="N5" s="357">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="355"/>
       <c r="P5" s="355"/>
@@ -12733,7 +12733,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -12761,7 +12761,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -13968,7 +13968,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -13996,7 +13996,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -15208,7 +15208,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -15236,7 +15236,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -19199,7 +19199,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -19227,7 +19227,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -20439,7 +20439,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -20467,7 +20467,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -21674,7 +21674,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -21702,7 +21702,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -22914,7 +22914,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -22942,7 +22942,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -24141,7 +24141,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -24162,7 +24162,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -25323,7 +25323,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -25344,7 +25344,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -26263,7 +26263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="316"/>
       <c r="C32" s="317"/>
       <c r="D32" s="317"/>
@@ -26505,7 +26505,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -26526,7 +26526,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -27451,7 +27451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="316"/>
       <c r="C32" s="317"/>
       <c r="D32" s="317"/>
@@ -27691,7 +27691,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -27712,7 +27712,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -28631,7 +28631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="316"/>
       <c r="C32" s="317"/>
       <c r="D32" s="317"/>
@@ -28873,7 +28873,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -28894,7 +28894,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -29813,7 +29813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="316"/>
       <c r="C32" s="317"/>
       <c r="D32" s="317"/>
@@ -30053,7 +30053,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -30073,7 +30073,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -30984,7 +30984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="316"/>
       <c r="C32" s="317"/>
       <c r="D32" s="317"/>
@@ -31237,7 +31237,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -31265,7 +31265,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -33002,7 +33002,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -33022,7 +33022,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -33933,7 +33933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="316"/>
       <c r="C32" s="317"/>
       <c r="D32" s="317"/>
@@ -34244,7 +34244,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -34272,7 +34272,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -35490,7 +35490,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -35518,7 +35518,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -36732,7 +36732,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -36760,7 +36760,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -37972,7 +37972,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -38000,7 +38000,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -39237,7 +39237,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -39265,7 +39265,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
@@ -40479,7 +40479,7 @@
       <c r="M4" s="330"/>
       <c r="N4" s="344">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="344"/>
       <c r="P4" s="344"/>
@@ -40507,7 +40507,7 @@
       <c r="M5" s="330"/>
       <c r="N5" s="344">
         <f ca="1">N4-1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="331"/>
       <c r="P5" s="331"/>
